--- a/output/pdf_financials_xlsx/RRCC.P.xlsx
+++ b/output/pdf_financials_xlsx/RRCC.P.xlsx
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.05985</v>
+        <v>-0.05985</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.137039</v>
+        <v>-0.137039</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.069142</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.05985</v>
+        <v>-0.05985</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.137039</v>
+        <v>-0.137039</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.069142</v>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.05985</v>
+        <v>-0.05985</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.137039</v>
+        <v>-0.137039</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.069142</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.05985</v>
+        <v>-0.05985</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.137039</v>
+        <v>-0.137039</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.069142</v>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.05985</v>
+        <v>-0.05985</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.137039</v>
+        <v>-0.137039</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.069142</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2251,16 +2251,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.018306</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.057952</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.057952</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.057952</v>
       </c>
     </row>
     <row r="93">
@@ -3406,7 +3406,11 @@
           <t>Reserve 3</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.018306</v>
       </c>
@@ -5127,13 +5131,13 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.137039</v>
+        <v>-0.137039</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.078872</v>
+        <v>-0.078872</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.069142</v>
+        <v>-0.069142</v>
       </c>
     </row>
     <row r="58">
@@ -5684,10 +5688,10 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0.05985</v>
+        <v>-0.05985</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.137039</v>
+        <v>-0.137039</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RRCC.P.xlsx
+++ b/output/pdf_financials_xlsx/RRCC.P.xlsx
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.134311</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.246601</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.180106</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.100867</v>
       </c>
     </row>
     <row r="35">
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.134311</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.246601</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.180106</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.100867</v>
       </c>
     </row>
     <row r="37">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
